--- a/20_VDJ/table/BCR_filtered_fol_freq.xlsx
+++ b/20_VDJ/table/BCR_filtered_fol_freq.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Fol</t>
   </si>
@@ -27,385 +27,112 @@
     <t xml:space="preserve">Fol-1</t>
   </si>
   <si>
-    <t xml:space="preserve">329</t>
+    <t xml:space="preserve">29</t>
   </si>
   <si>
     <t xml:space="preserve">Fol-2</t>
   </si>
   <si>
-    <t xml:space="preserve">347</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-3</t>
   </si>
   <si>
-    <t xml:space="preserve">233</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-4</t>
   </si>
   <si>
-    <t xml:space="preserve">202</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-5</t>
   </si>
   <si>
-    <t xml:space="preserve">252</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-6</t>
   </si>
   <si>
-    <t xml:space="preserve">301</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-7</t>
   </si>
   <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-8</t>
   </si>
   <si>
-    <t xml:space="preserve">91</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-9</t>
   </si>
   <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-10</t>
   </si>
   <si>
     <t xml:space="preserve">Fol-11</t>
   </si>
   <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-12</t>
   </si>
   <si>
-    <t xml:space="preserve">98</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-13</t>
   </si>
   <si>
-    <t xml:space="preserve">223</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-14</t>
   </si>
   <si>
-    <t xml:space="preserve">105</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-15</t>
   </si>
   <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-16</t>
   </si>
   <si>
-    <t xml:space="preserve">135</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-17</t>
   </si>
   <si>
-    <t xml:space="preserve">97</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-18</t>
   </si>
   <si>
-    <t xml:space="preserve">336</t>
-  </si>
-  <si>
     <t xml:space="preserve">Negative</t>
   </si>
   <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
     <t xml:space="preserve">Doublet</t>
   </si>
   <si>
-    <t xml:space="preserve">494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-19</t>
   </si>
   <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-20</t>
   </si>
   <si>
-    <t xml:space="preserve">393</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-21</t>
   </si>
   <si>
-    <t xml:space="preserve">193</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-22</t>
   </si>
   <si>
-    <t xml:space="preserve">1335</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-23</t>
   </si>
   <si>
-    <t xml:space="preserve">771</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-24</t>
   </si>
   <si>
-    <t xml:space="preserve">1157</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-25</t>
   </si>
   <si>
-    <t xml:space="preserve">945</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-26</t>
   </si>
   <si>
-    <t xml:space="preserve">261</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-27</t>
   </si>
   <si>
-    <t xml:space="preserve">561</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-28</t>
   </si>
   <si>
     <t xml:space="preserve">Fol-29</t>
   </si>
   <si>
-    <t xml:space="preserve">560</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-30</t>
   </si>
   <si>
-    <t xml:space="preserve">259</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-31</t>
   </si>
   <si>
-    <t xml:space="preserve">339</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-32</t>
   </si>
   <si>
-    <t xml:space="preserve">190</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-33</t>
   </si>
   <si>
-    <t xml:space="preserve">486</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fol-34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
   </si>
 </sst>
 </file>
@@ -755,151 +482,151 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +653,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -934,143 +661,143 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1094,154 +821,154 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +995,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1276,143 +1003,143 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1436,154 +1163,154 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/20_VDJ/table/BCR_filtered_fol_freq.xlsx
+++ b/20_VDJ/table/BCR_filtered_fol_freq.xlsx
@@ -7,16 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="HH117" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HH119-CD19-Pool1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="HH119-CD19-Pool2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HH119-GC-AND-PB-AND-TFH-Pool1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="HH119-GC-AND-PB-AND-TFH-Pool2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="HH119" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t xml:space="preserve">Fol</t>
   </si>
@@ -27,112 +24,256 @@
     <t xml:space="preserve">Fol-1</t>
   </si>
   <si>
-    <t xml:space="preserve">29</t>
+    <t xml:space="preserve">329</t>
   </si>
   <si>
     <t xml:space="preserve">Fol-2</t>
   </si>
   <si>
+    <t xml:space="preserve">347</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-3</t>
   </si>
   <si>
+    <t xml:space="preserve">233</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-4</t>
   </si>
   <si>
+    <t xml:space="preserve">202</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-5</t>
   </si>
   <si>
+    <t xml:space="preserve">252</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-6</t>
   </si>
   <si>
+    <t xml:space="preserve">301</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-7</t>
   </si>
   <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-8</t>
   </si>
   <si>
+    <t xml:space="preserve">91</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-9</t>
   </si>
   <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-10</t>
   </si>
   <si>
     <t xml:space="preserve">Fol-11</t>
   </si>
   <si>
+    <t xml:space="preserve">85</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-12</t>
   </si>
   <si>
+    <t xml:space="preserve">98</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-13</t>
   </si>
   <si>
+    <t xml:space="preserve">223</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-14</t>
   </si>
   <si>
+    <t xml:space="preserve">105</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-15</t>
   </si>
   <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-16</t>
   </si>
   <si>
+    <t xml:space="preserve">135</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-17</t>
   </si>
   <si>
+    <t xml:space="preserve">97</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Negative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doublet</t>
+    <t xml:space="preserve">336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283</t>
   </si>
   <si>
     <t xml:space="preserve">Fol-19</t>
   </si>
   <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-20</t>
   </si>
   <si>
+    <t xml:space="preserve">492</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-21</t>
   </si>
   <si>
+    <t xml:space="preserve">230</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-22</t>
   </si>
   <si>
+    <t xml:space="preserve">3289</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-23</t>
   </si>
   <si>
+    <t xml:space="preserve">953</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-24</t>
   </si>
   <si>
+    <t xml:space="preserve">1513</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-25</t>
   </si>
   <si>
+    <t xml:space="preserve">1262</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-26</t>
   </si>
   <si>
+    <t xml:space="preserve">309</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-27</t>
   </si>
   <si>
+    <t xml:space="preserve">667</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-28</t>
   </si>
   <si>
+    <t xml:space="preserve">1060</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-29</t>
   </si>
   <si>
+    <t xml:space="preserve">850</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-30</t>
   </si>
   <si>
+    <t xml:space="preserve">318</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-31</t>
   </si>
   <si>
+    <t xml:space="preserve">441</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-32</t>
   </si>
   <si>
+    <t xml:space="preserve">219</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-33</t>
   </si>
   <si>
+    <t xml:space="preserve">547</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fol-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1921</t>
   </si>
 </sst>
 </file>
@@ -482,151 +623,135 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -653,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -661,656 +786,263 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
